--- a/test/session--package-of-documents/reference/15 subjects/Відомості.xlsx
+++ b/test/session--package-of-documents/reference/15 subjects/Відомості.xlsx
@@ -31,7 +31,7 @@
     <definedName name="Ф80" localSheetId="4">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Рейтингова D7'!$C$3:$V$25</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
